--- a/大学物理实验/实验五 用模拟法测量静电场/实验5 用模拟法测量静电场.xlsx
+++ b/大学物理实验/实验五 用模拟法测量静电场/实验5 用模拟法测量静电场.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\笔记\大学物理实验\实验五 用模拟法测量静电场\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871E9DD1-EA0C-46C1-819B-C504C1B757FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF2C6DB-9774-49AB-890A-4B5AD3357C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{7D63F694-6260-4984-98C1-960E1E77DB64}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D63F694-6260-4984-98C1-960E1E77DB64}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -208,11 +206,71 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>Vr/Vb-lnr/ln7</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>图</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -247,48 +305,122 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
-          <c:cat>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="6.8350962906745097E-2"/>
+                  <c:y val="-4.3369772661913518E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-CN"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$J$4:$J$10</c:f>
               <c:numCache>
                 <c:formatCode>0.000_ </c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0.15040242947748797</c:v>
+                  <c:v>0.21178246643448623</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.36487003162558967</c:v>
+                  <c:v>0.30999502897130504</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.36989843125891736</c:v>
+                  <c:v>0.4121472853519868</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.49083805648633955</c:v>
+                  <c:v>0.52801731947057318</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.58817783601784146</c:v>
+                  <c:v>0.61604038493504643</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.69277255630438328</c:v>
+                  <c:v>0.71803639126736885</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.80029499757201028</c:v>
+                  <c:v>0.81365486252952357</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:cat>
-          <c:val>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
               <c:f>Sheet1!$A$4:$A$10</c:f>
               <c:numCache>
@@ -317,7 +449,7 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -333,11 +465,10 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
         <c:axId val="1867662976"/>
         <c:axId val="1867646656"/>
-      </c:lineChart>
-      <c:catAx>
+      </c:scatterChart>
+      <c:valAx>
         <c:axId val="1867662976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
@@ -443,11 +574,8 @@
         </c:txPr>
         <c:crossAx val="1867646656"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
       <c:valAx>
         <c:axId val="1867646656"/>
         <c:scaling>
@@ -558,7 +686,7 @@
         </c:txPr>
         <c:crossAx val="1867662976"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1527,12 +1655,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C68F33-5CD3-4936-9C0C-50001705C291}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="10" max="10" width="10.75" customWidth="1"/>
+    <col min="10" max="10" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="38.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="38.549999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>11</v>
       </c>
@@ -1546,7 +1674,7 @@
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -1560,7 +1688,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1592,256 +1720,256 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>0.2</v>
       </c>
       <c r="B4" s="1">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="C4" s="1">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="D4" s="1">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="E4" s="1">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="F4" s="1">
-        <v>2.69</v>
+        <v>2.99</v>
       </c>
       <c r="G4" s="1">
         <f>AVERAGE(B4:F4)</f>
-        <v>2.6799999999999997</v>
+        <v>3.02</v>
       </c>
       <c r="H4" s="1">
         <f>G4/2</f>
-        <v>1.3399999999999999</v>
+        <v>1.51</v>
       </c>
       <c r="I4" s="1">
         <f>LN(H4)</f>
-        <v>0.29266961396281987</v>
+        <v>0.41210965082683298</v>
       </c>
       <c r="J4" s="2">
         <f>I4/LN(7)</f>
-        <v>0.15040242947748797</v>
+        <v>0.21178246643448623</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>0.3</v>
       </c>
       <c r="B5" s="1">
-        <v>3.37</v>
+        <v>3.58</v>
       </c>
       <c r="C5" s="1">
+        <v>3.65</v>
+      </c>
+      <c r="D5" s="1">
         <v>3.5</v>
       </c>
-      <c r="D5" s="1">
-        <v>6.46</v>
-      </c>
       <c r="E5" s="1">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="F5" s="1">
-        <v>3.46</v>
+        <v>3.75</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" ref="G5:G10" si="0">AVERAGE(B5:F5)</f>
-        <v>4.0679999999999996</v>
+        <v>3.6560000000000001</v>
       </c>
       <c r="H5" s="1">
         <f t="shared" ref="H5:H10" si="1">G5/2</f>
-        <v>2.0339999999999998</v>
+        <v>1.8280000000000001</v>
       </c>
       <c r="I5" s="1">
         <f t="shared" ref="I5:I10" si="2">LN(H5)</f>
-        <v>0.71000429762636807</v>
+        <v>0.60322247303195831</v>
       </c>
       <c r="J5" s="2">
         <f t="shared" ref="J5:J10" si="3">I5/LN(7)</f>
-        <v>0.36487003162558967</v>
+        <v>0.30999502897130504</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>0.4</v>
       </c>
       <c r="B6" s="1">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="C6" s="1">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="D6" s="1">
-        <v>4.18</v>
+        <v>4.3</v>
       </c>
       <c r="E6" s="1">
-        <v>4.26</v>
+        <v>4.55</v>
       </c>
       <c r="F6" s="1">
-        <v>4.1500000000000004</v>
+        <v>4.45</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="0"/>
-        <v>4.1079999999999997</v>
+        <v>4.46</v>
       </c>
       <c r="H6" s="1">
         <f t="shared" si="1"/>
-        <v>2.0539999999999998</v>
+        <v>2.23</v>
       </c>
       <c r="I6" s="1">
         <f t="shared" si="2"/>
-        <v>0.71978911150636637</v>
+        <v>0.80200158547202738</v>
       </c>
       <c r="J6" s="2">
         <f t="shared" si="3"/>
-        <v>0.36989843125891736</v>
+        <v>0.4121472853519868</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>0.5</v>
       </c>
       <c r="B7" s="1">
-        <v>5.0999999999999996</v>
+        <v>5.6</v>
       </c>
       <c r="C7" s="1">
-        <v>5.23</v>
+        <v>5.65</v>
       </c>
       <c r="D7" s="1">
-        <v>5.16</v>
+        <v>5.4</v>
       </c>
       <c r="E7" s="1">
-        <v>5.35</v>
+        <v>5.69</v>
       </c>
       <c r="F7" s="1">
-        <v>5.15</v>
+        <v>5.6</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="0"/>
-        <v>5.1980000000000004</v>
+        <v>5.5879999999999992</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" si="1"/>
-        <v>2.5990000000000002</v>
+        <v>2.7939999999999996</v>
       </c>
       <c r="I7" s="1">
         <f t="shared" si="2"/>
-        <v>0.95512675565935323</v>
+        <v>1.02747426083477</v>
       </c>
       <c r="J7" s="2">
         <f t="shared" si="3"/>
-        <v>0.49083805648633955</v>
+        <v>0.52801731947057318</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>0.6</v>
       </c>
       <c r="B8" s="1">
-        <v>6.2</v>
+        <v>6.61</v>
       </c>
       <c r="C8" s="1">
-        <v>6.28</v>
+        <v>6.71</v>
       </c>
       <c r="D8" s="1">
-        <v>6.29</v>
+        <v>6.59</v>
       </c>
       <c r="E8" s="1">
-        <v>6.37</v>
+        <v>6.65</v>
       </c>
       <c r="F8" s="1">
-        <v>6.27</v>
+        <v>6.6</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="0"/>
-        <v>6.282</v>
+        <v>6.6320000000000006</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="1"/>
-        <v>3.141</v>
+        <v>3.3160000000000003</v>
       </c>
       <c r="I8" s="1">
         <f t="shared" si="2"/>
-        <v>1.1445412205565095</v>
+        <v>1.1987592372730487</v>
       </c>
       <c r="J8" s="2">
         <f t="shared" si="3"/>
-        <v>0.58817783601784146</v>
+        <v>0.61604038493504643</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>0.7</v>
       </c>
       <c r="B9" s="1">
-        <v>7.75</v>
+        <v>8.09</v>
       </c>
       <c r="C9" s="1">
-        <v>7.71</v>
+        <v>8.1</v>
       </c>
       <c r="D9" s="1">
-        <v>7.66</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1">
-        <v>7.71</v>
+        <v>8.15</v>
       </c>
       <c r="F9" s="1">
-        <v>7.67</v>
+        <v>8.1</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="0"/>
-        <v>7.7</v>
+        <v>8.0879999999999992</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="1"/>
-        <v>3.85</v>
+        <v>4.0439999999999996</v>
       </c>
       <c r="I9" s="1">
         <f t="shared" si="2"/>
-        <v>1.3480731482996928</v>
+        <v>1.3972343011582249</v>
       </c>
       <c r="J9" s="2">
         <f t="shared" si="3"/>
-        <v>0.69277255630438328</v>
+        <v>0.71803639126736885</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>0.8</v>
       </c>
       <c r="B10" s="1">
-        <v>9.52</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="C10" s="1">
-        <v>9.6300000000000008</v>
+        <v>9.75</v>
       </c>
       <c r="D10" s="1">
-        <v>9.5</v>
+        <v>9.65</v>
       </c>
       <c r="E10" s="1">
-        <v>9.56</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="F10" s="1">
-        <v>9.25</v>
+        <v>9.82</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="0"/>
-        <v>9.4920000000000009</v>
+        <v>9.7420000000000009</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="1"/>
-        <v>4.7460000000000004</v>
+        <v>4.8710000000000004</v>
       </c>
       <c r="I10" s="1">
         <f t="shared" si="2"/>
-        <v>1.557302158013572</v>
+        <v>1.5832992548244056</v>
       </c>
       <c r="J10" s="2">
         <f t="shared" si="3"/>
-        <v>0.80029499757201028</v>
+        <v>0.81365486252952357</v>
       </c>
     </row>
   </sheetData>
